--- a/links de interes.xlsx
+++ b/links de interes.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="91">
   <si>
     <t>Enlace</t>
   </si>
@@ -286,6 +286,12 @@
   </si>
   <si>
     <t>Otros ejemplos de funciones</t>
+  </si>
+  <si>
+    <t>https://mvnrepository.com/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dependencias MAVEN </t>
   </si>
 </sst>
 </file>
@@ -626,7 +632,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:C48"/>
+  <dimension ref="B2:C49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="64.28515625" bestFit="1" customWidth="1"/>
@@ -1004,6 +1010,14 @@
       </c>
       <c r="C48" t="s">
         <v>88</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B49" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C49" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -1054,8 +1068,9 @@
     <hyperlink ref="B46" r:id="rId44"/>
     <hyperlink ref="B47" r:id="rId45"/>
     <hyperlink ref="B48" r:id="rId46"/>
+    <hyperlink ref="B49" r:id="rId47"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId47"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId48"/>
 </worksheet>
 </file>